--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -59,55 +59,37 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
+    <t xml:space="preserve">Eden Park, Auckland</t>
   </si>
 </sst>
 </file>
@@ -446,8 +428,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -456,7 +438,7 @@
     <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="26.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="23.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -506,7 +488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -518,16 +500,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.7</v>
+        <v>-1.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7</v>
+        <v>-1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.7</v>
+        <v>-1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>57.3</v>
+        <v>48.1</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -539,18 +521,18 @@
         <v>-7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>48</v>
+        <v>45.5</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -562,16 +544,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.7</v>
+        <v>-1.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7</v>
+        <v>-1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.7</v>
+        <v>-1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>57.2</v>
+        <v>48.1</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -583,18 +565,18 @@
         <v>-7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>48</v>
+        <v>45.5</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -606,16 +588,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.8</v>
+        <v>-0.6</v>
       </c>
       <c r="H4" t="n">
-        <v>28.6</v>
+        <v>24.1</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -627,18 +609,18 @@
         <v>-7.5</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>45.5</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46276</v>
+        <v>46284</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -650,16 +632,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8</v>
+        <v>-0.6</v>
       </c>
       <c r="H5" t="n">
-        <v>28.6</v>
+        <v>24.1</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -671,18 +653,18 @@
         <v>-7.5</v>
       </c>
       <c r="L5" t="n">
-        <v>48</v>
+        <v>45.5</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -694,16 +676,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>-5</v>
+        <v>-10.2</v>
       </c>
       <c r="H6" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -712,21 +694,21 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -738,16 +720,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-5</v>
+        <v>-10.2</v>
       </c>
       <c r="H7" t="n">
-        <v>52.3</v>
+        <v>51.1</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -756,21 +738,21 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="L7" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -782,16 +764,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4</v>
+        <v>-3.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4</v>
+        <v>-3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5</v>
+        <v>-5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -800,21 +782,21 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -826,16 +808,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4</v>
+        <v>-3.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4</v>
+        <v>-3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5</v>
+        <v>-5.1</v>
       </c>
       <c r="H9" t="n">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -844,368 +826,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H10" t="n">
-        <v>54</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H11" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="I11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L11" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M11" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>27</v>
-      </c>
-      <c r="I12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M12" t="s">
-        <v>19</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M14" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="I15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M15" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L16" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M16" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I17" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M17" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -59,19 +59,19 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
     <t xml:space="preserve">FT</t>
   </si>
   <si>
     <t xml:space="preserve">No Rain</t>
   </si>
   <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
   </si>
   <si>
     <t xml:space="preserve">Weather Adjusted</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">1H</t>
   </si>
   <si>
-    <t xml:space="preserve">18:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">Eden Park, Auckland</t>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -428,8 +428,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -438,7 +438,7 @@
     <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="23.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="25.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,7 +488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -500,16 +500,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>48.1</v>
+        <v>49.8</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -518,10 +518,10 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -532,7 +532,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -544,16 +544,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>48.1</v>
+        <v>49.8</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -562,10 +562,10 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -588,16 +588,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -606,10 +606,10 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L4" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
@@ -620,7 +620,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -632,16 +632,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -676,16 +676,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.4</v>
+        <v>-7.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.4</v>
+        <v>-7.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.2</v>
+        <v>-7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>51.4</v>
+        <v>44.6</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -694,21 +694,21 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L6" t="n">
-        <v>44.5</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -720,16 +720,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.4</v>
+        <v>-7.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.4</v>
+        <v>-7.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.2</v>
+        <v>-7.5</v>
       </c>
       <c r="H7" t="n">
-        <v>51.1</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -738,21 +738,21 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L7" t="n">
-        <v>44.5</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -764,16 +764,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.1</v>
+        <v>-3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>25.7</v>
+        <v>22.3</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -782,21 +782,21 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L8" t="n">
-        <v>44.5</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -808,16 +808,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.1</v>
+        <v>-3.8</v>
       </c>
       <c r="H9" t="n">
-        <v>25.5</v>
+        <v>21.5</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -826,16 +826,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,40 +56,28 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
+    <t xml:space="preserve">19:30</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">FT</t>
   </si>
   <si>
     <t xml:space="preserve">No Rain</t>
   </si>
   <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
   </si>
   <si>
     <t xml:space="preserve">Weather Adjusted</t>
   </si>
   <si>
     <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -428,7 +416,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -438,7 +426,7 @@
     <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="25.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="21.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,7 +476,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -500,16 +488,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>-8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>-8</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.4</v>
+        <v>-7.9</v>
       </c>
       <c r="H2" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -518,10 +506,10 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.5</v>
+        <v>-7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -532,7 +520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -544,16 +532,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>-8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>-8</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.4</v>
+        <v>-7.9</v>
       </c>
       <c r="H3" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -562,10 +550,10 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5</v>
+        <v>-7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
@@ -576,7 +564,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -588,16 +576,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>-4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>-4</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2</v>
+        <v>-3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -606,10 +594,10 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.5</v>
+        <v>-7.5</v>
       </c>
       <c r="L4" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
@@ -620,7 +608,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -632,16 +620,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>-4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>-4</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2</v>
+        <v>-3.9</v>
       </c>
       <c r="H5" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -650,192 +638,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.5</v>
+        <v>-7.5</v>
       </c>
       <c r="L5" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>43</v>
-      </c>
-      <c r="I7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>41</v>
-      </c>
-      <c r="M7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>41</v>
-      </c>
-      <c r="M8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>41</v>
-      </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7.3</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -488,16 +488,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" t="n">
         <v>-8</v>
       </c>
-      <c r="F2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-7.9</v>
-      </c>
       <c r="H2" t="n">
-        <v>49.1</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -532,16 +532,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="G3" t="n">
         <v>-8</v>
       </c>
-      <c r="F3" t="n">
-        <v>-8</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-7.9</v>
-      </c>
       <c r="H3" t="n">
-        <v>49.1</v>
+        <v>48</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -576,16 +576,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G4" t="n">
         <v>-4</v>
       </c>
-      <c r="F4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-3.9</v>
-      </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -620,16 +620,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G5" t="n">
         <v>-4</v>
       </c>
-      <c r="F5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-3.9</v>
-      </c>
       <c r="H5" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
